--- a/prospecting/03_Pipeline_CRM.xlsx
+++ b/prospecting/03_Pipeline_CRM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bce441479ebfac8e/Desktop/ArthaInvest/prospecting/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artha\OneDrive\Desktop\ArthaInvest\prospecting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{286B8A07-C1A8-4344-8833-97B62FB11B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBD4DC70-9168-466C-878A-E0C592E94728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{35ADD0E2-6156-4994-9FC5-215A6351EA50}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{1D7893EB-5F78-4FAB-BC96-C3551240D2A7}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{578182F7-5B72-4D2E-8C03-E4AB5962D5AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEA75F3-4244-42C4-8B84-D729B1F15254}">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>46255.390972222223</v>
+        <v>46268.388194444444</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -903,7 +903,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40E86783-F770-4E94-9E66-45442958439D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF2F7C4-634F-4C8E-A780-DF8C76B6CF3D}">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1464,7 +1464,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{40E86783-F770-4E94-9E66-45442958439D}"/>
+  <autoFilter ref="A1:Q1" xr:uid="{CCF2F7C4-634F-4C8E-A780-DF8C76B6CF3D}"/>
   <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>LEN(K2)&gt;0</formula>
@@ -1475,7 +1475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E606A62B-E54F-422D-BCB9-334BECDF033C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF04C8C-4A7F-4B06-B52B-4F15A785BE7F}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1635,7 +1635,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{E606A62B-E54F-422D-BCB9-334BECDF033C}"/>
+  <autoFilter ref="A1:I1" xr:uid="{CFF04C8C-4A7F-4B06-B52B-4F15A785BE7F}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/prospecting/03_Pipeline_CRM.xlsx
+++ b/prospecting/03_Pipeline_CRM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artha\OneDrive\Desktop\ArthaInvest\prospecting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBD4DC70-9168-466C-878A-E0C592E94728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{94023D11-D7DB-436A-8F86-43815D0DCECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14400" windowHeight="7270" xr2:uid="{1D7893EB-5F78-4FAB-BC96-C3551240D2A7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E9E04EA0-3558-417B-BDD2-79C9A490794E}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -755,7 +755,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEEA75F3-4244-42C4-8B84-D729B1F15254}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7287E76A-D7A9-4A42-85DB-51452032538C}">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -773,7 +773,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>46268.388194444444</v>
+        <v>46270.703472222223</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -903,7 +903,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCF2F7C4-634F-4C8E-A780-DF8C76B6CF3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2AE274-7746-4E2E-BE54-A417BBD5C037}">
   <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1464,7 +1464,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1" xr:uid="{CCF2F7C4-634F-4C8E-A780-DF8C76B6CF3D}"/>
+  <autoFilter ref="A1:Q1" xr:uid="{4B2AE274-7746-4E2E-BE54-A417BBD5C037}"/>
   <conditionalFormatting sqref="K2:K13">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>LEN(K2)&gt;0</formula>
@@ -1475,7 +1475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFF04C8C-4A7F-4B06-B52B-4F15A785BE7F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA45CD63-B0B6-42E2-99D0-6C4AA439F11C}">
   <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1635,7 +1635,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{CFF04C8C-4A7F-4B06-B52B-4F15A785BE7F}"/>
+  <autoFilter ref="A1:I1" xr:uid="{DA45CD63-B0B6-42E2-99D0-6C4AA439F11C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>